--- a/catalogo_template.xlsx
+++ b/catalogo_template.xlsx
@@ -473,7 +473,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -540,7 +540,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/edilizia-ferramenta/EF-FER-001.jpg</t>
+          <t>EF-FER-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/edilizia-ferramenta/EF-LUC-001.jpg</t>
+          <t>EF-LUC-001</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/edilizia-ferramenta/EF-SCA-001.jpg</t>
+          <t>EF-SCA-001</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/edilizia-ferramenta/EF-SCA-002.jpg</t>
+          <t>EF-SCA-002</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/edilizia-ferramenta/EF-ALT-001.jpg</t>
+          <t>EF-ALT-001</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -700,7 +700,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -767,7 +767,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-PRE-001.jpg</t>
+          <t>EL-PRE-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-ILL-001.jpg</t>
+          <t>EL-ILL-001</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-MUL-001.jpg</t>
+          <t>EL-MUL-001</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-MUL-002.jpg</t>
+          <t>EL-MUL-002</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-MUL-003.jpg</t>
+          <t>EL-MUL-003</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettricita/EL-MUL-004.jpg</t>
+          <t>EL-MUL-004</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -954,7 +954,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-001.jpg</t>
+          <t>ED-FRI-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-002.jpg</t>
+          <t>ED-FRI-002</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-003.jpg</t>
+          <t>ED-FRI-003</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-004.jpg</t>
+          <t>ED-FRI-004</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-005.jpg</t>
+          <t>ED-FRI-005</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-006.jpg</t>
+          <t>ED-FRI-006</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-007.jpg</t>
+          <t>ED-FRI-007</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-008.jpg</t>
+          <t>ED-FRI-008</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-009.jpg</t>
+          <t>ED-FRI-009</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-LAV-001.jpg</t>
+          <t>ED-LAV-001</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-LAV-002.jpg</t>
+          <t>ED-LAV-002</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-LAV-003.jpg</t>
+          <t>ED-LAV-003</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-LAV-004.jpg</t>
+          <t>ED-LAV-004</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-LAV-005.jpg</t>
+          <t>ED-LAV-005</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-TEL-001.jpg</t>
+          <t>ED-TEL-001</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-TEL-002.jpg</t>
+          <t>ED-TEL-002</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-TEL-003.jpg</t>
+          <t>ED-TEL-003</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-PIC-001.jpg</t>
+          <t>ED-PIC-001</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-INC-001.jpg</t>
+          <t>ED-INC-001</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-INC-002.jpg</t>
+          <t>ED-INC-002</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettrodomestici/ED-FRI-010.jpg</t>
+          <t>ED-FRI-010</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-TRA-001.jpg</t>
+          <t>EU-TRA-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-TRA-002.jpg</t>
+          <t>EU-TRA-002</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-TRA-003.jpg</t>
+          <t>EU-TRA-003</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-TRA-004.jpg</t>
+          <t>EU-TRA-004</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-TRA-005.jpg</t>
+          <t>EU-TRA-005</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-SEG-001.jpg</t>
+          <t>EU-SEG-001</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-LEV-001.jpg</t>
+          <t>EU-LEV-001</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-LEV-002.jpg</t>
+          <t>EU-LEV-002</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-LEV-003.jpg</t>
+          <t>EU-LEV-003</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-SME-001.jpg</t>
+          <t>EU-SME-001</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-SME-002.jpg</t>
+          <t>EU-SME-002</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-BAT-001.jpg</t>
+          <t>EU-BAT-001</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-BAT-002.jpg</t>
+          <t>EU-BAT-002</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-ALT-001.jpg</t>
+          <t>EU-ALT-001</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>assets/img/elettroutensili/EU-ALT-002.jpg</t>
+          <t>EU-ALT-002</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/idraulica/ID-PRC-001.jpg</t>
+          <t>ID-PRC-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/idraulica/ID-DOC-001.jpg</t>
+          <t>ID-DOC-001</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="93" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-CHI-001.jpg</t>
+          <t>UM-CHI-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-CHI-002.jpg</t>
+          <t>UM-CHI-002</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-CAC-001.jpg</t>
+          <t>UM-CAC-001</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-CAC-002.jpg</t>
+          <t>UM-CAC-002</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-CAC-003.jpg</t>
+          <t>UM-CAC-003</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-PIN-001.jpg</t>
+          <t>UM-PIN-001</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-PIN-002.jpg</t>
+          <t>UM-PIN-002</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-MET-001.jpg</t>
+          <t>UM-MET-001</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-TAG-001.jpg</t>
+          <t>UM-TAG-001</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-ALT-001.jpg</t>
+          <t>UM-ALT-001</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>assets/img/utensili-manuali/UM-ALT-002.jpg</t>
+          <t>UM-ALT-002</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -2804,7 +2804,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="43" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="107" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vernici-colori/VC-PEN-001.jpg</t>
+          <t>VC-PEN-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vernici-colori/VC-PEN-002.jpg</t>
+          <t>VC-PEN-002</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -2942,7 +2942,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="68" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-CAS-001.jpg</t>
+          <t>VA-CAS-001</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-CAS-002.jpg</t>
+          <t>VA-CAS-002</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-GIA-001.jpg</t>
+          <t>VA-GIA-001</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-GIA-002.jpg</t>
+          <t>VA-GIA-002</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-GIA-003.jpg</t>
+          <t>VA-GIA-003</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-GIA-004.jpg</t>
+          <t>VA-GIA-004</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>assets/img/vario/VA-GIA-005.jpg</t>
+          <t>VA-GIA-005</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>

--- a/catalogo_template.xlsx
+++ b/catalogo_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aless\Desktop\ferramentaballini\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F8AC7A-9D38-4B70-8452-CCC160C5E20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A420A0F-79C5-4650-ABAF-12F6F5EDFAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edilizia e ferramenta" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="264">
   <si>
     <t>Codice Prodotto</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Prezzo Base</t>
   </si>
   <si>
-    <t>Disponibilità</t>
-  </si>
-  <si>
     <t>Immagine</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>Ferramenta varia</t>
   </si>
   <si>
-    <t>Disponibile</t>
-  </si>
-  <si>
     <t>EF-LUC-001</t>
   </si>
   <si>
@@ -102,6 +96,24 @@
     <t>Altro</t>
   </si>
   <si>
+    <t>Tassello nylon 'GL-5VPS' c/vite 4,0 x 30 '65005'</t>
+  </si>
+  <si>
+    <t>Tasselli e ancoraggi</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/EF0002/gallery_0002.jpg</t>
+  </si>
+  <si>
+    <t>Convertiruggine FEROX</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/920010/gallery_ferox-convertiruggine-ml-95-art-4143.jpg | https://b2b.dfl.it//sites/default/files//product_images/920011/gallery_ferox-convertiruggine-ml-375-art-4148.jpg | https://b2b.dfl.it//sites/default/files//product_images/920012/gallery_ferox-convertiruggine-ml-750-art-4145.jpg</t>
+  </si>
+  <si>
+    <t>varianti: 95 ml = xx.xx | 375 ml = xx.xx | 750 ml = xx.xx</t>
+  </si>
+  <si>
     <t>EL-PRE-001</t>
   </si>
   <si>
@@ -147,6 +159,30 @@
     <t>Adattatore multipresa USB ELETTROCANALI</t>
   </si>
   <si>
+    <t>Lampadina LED 'sfera' 8 W E14</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0380/gallery_0380.jpg</t>
+  </si>
+  <si>
+    <t>Lampadina LED 'oliva' 8 W 806 LM-6500K fredda 60 W</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0389/gallery_0389.jpg</t>
+  </si>
+  <si>
+    <t>Lampada LED 'spot' GU10/6 W 490 LM-4000K naturale 40 W</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0394/gallery_0394.jpg</t>
+  </si>
+  <si>
+    <t>Adattatore 2+1 schuko 2P+T10A SP.2P+T10A</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0187/gallery_0187.jpg</t>
+  </si>
+  <si>
     <t>ED-FRI-001</t>
   </si>
   <si>
@@ -156,9 +192,6 @@
     <t>Frigoriferi e congelatori</t>
   </si>
   <si>
-    <t>Contattare Negozio</t>
-  </si>
-  <si>
     <t>ED-FRI-002</t>
   </si>
   <si>
@@ -276,7 +309,7 @@
     <t>Lavatrice incasso INDESIT - 7 kg, 1200 G</t>
   </si>
   <si>
-    <t>elettrodomestici da incasso</t>
+    <t>Elettrodomestici da incasso</t>
   </si>
   <si>
     <t>ED-INC-002</t>
@@ -291,6 +324,12 @@
     <t>Minifrigo da hotel MELCHIONI - 4.5 LT, 43.7 X 47 X 49.5 cm</t>
   </si>
   <si>
+    <t>Fornello elettrico 2 piastre - 1500 + 1000 W, D. 15,5 + 18,5 c/termost. regol.</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/CA2008/gallery_fornello-elettrico-2-piastre-1500-1000w-d-15-5-18-5-c-termost-regol.jpg</t>
+  </si>
+  <si>
     <t>EU-TRA-001</t>
   </si>
   <si>
@@ -399,6 +438,21 @@
     <t>Pistolia ad aria calda 'RF18-A2' VULPOWER - 1000/2000 W</t>
   </si>
   <si>
+    <t>Punta widia 'SDX' 4 x 75 mm per muro FISCHER</t>
+  </si>
+  <si>
+    <t>Accessori</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/UM0091/gallery_0091.jpg</t>
+  </si>
+  <si>
+    <t>Punta carburo 'S-SDX' 5 x 85 mm 4 taglienti FISCHER</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/UM0092/gallery_0092.jpg</t>
+  </si>
+  <si>
     <t>ID-PRC-001</t>
   </si>
   <si>
@@ -522,6 +576,9 @@
     <t>varianti: lama 9 mm = 3.60 | lama 18 mm = 5.40</t>
   </si>
   <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/UM1521/gallery_pistola-per-silicone-a-frizione-uniko-all-e-ferro.jpg</t>
+  </si>
+  <si>
     <t>VC-PEN-001</t>
   </si>
   <si>
@@ -543,6 +600,36 @@
     <t>numero: N.20 = 0.90 | N.30 = 1.00 | N.40 = 1.20 | N.50 = 1.50 | N.60 = 1.90 | N.70 = 2.10 | N.100 = 3.50</t>
   </si>
   <si>
+    <t>Isolante fissativo ad acqua antimuffa bianco polare - 4 LT</t>
+  </si>
+  <si>
+    <t>Vernici speciali</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/9008764/gallery_isolante-fissativo-ad-acqua-lt-4-antimuffa-bianco-polare.jpg</t>
+  </si>
+  <si>
+    <t>Stucco 'K2' in polvere per interni - 20 kg</t>
+  </si>
+  <si>
+    <t>Stucchi e siliconi</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0164/gallery_0164.jpg</t>
+  </si>
+  <si>
+    <t>Stucco 'super stucco' 'fassa bortolo' - 10 kg</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0710/gallery_0710.jpg</t>
+  </si>
+  <si>
+    <t>Idropittura bianco polare antimuffa - 4 LT, semilavabile per interni, trasp.</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0136/gallery_0136.jpg</t>
+  </si>
+  <si>
     <t>VA-CAS-001</t>
   </si>
   <si>
@@ -594,6 +681,30 @@
     <t>Tubo estensibile per giardino da 7.5 m a 22.5 m LIF</t>
   </si>
   <si>
+    <t>Appendiabito doppio 'Dubbel' - cm 80 x 42 x H90 c/ruote nero</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/FE1240/gallery_1240.jpg</t>
+  </si>
+  <si>
+    <t>Maniglia goccia c/ros. bocchetta cromo satinato</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/3020052/gallery_maniglia-goccia-c-ros-bocchetta-cromo-satinato.jpg</t>
+  </si>
+  <si>
+    <t>Carbone vegetale per grill - 5 kg</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/700872/gallery_carbone-vegetale-x-grill-kg-5-ca-in-sacchi.jpg</t>
+  </si>
+  <si>
+    <t>Insetticida spray per vespe - 750 ml</t>
+  </si>
+  <si>
+    <t>https://b2b.dfl.it//sites/default/files//product_images/TL0768/gallery_0768.jpg</t>
+  </si>
+  <si>
     <t>Edilizia e ferramenta</t>
   </si>
   <si>
@@ -618,193 +729,97 @@
     <t>Vario</t>
   </si>
   <si>
-    <t>Materiale edile</t>
-  </si>
-  <si>
-    <t>Chiavi e serraggio</t>
-  </si>
-  <si>
-    <t>Vernici e smalti</t>
+    <t>Viti e bulloneria</t>
   </si>
   <si>
     <t>Cavi e prolunghe</t>
   </si>
   <si>
-    <t>Cottura e forni</t>
-  </si>
-  <si>
     <t>Tubi e raccordi</t>
   </si>
   <si>
-    <t>Giraviti</t>
-  </si>
-  <si>
-    <t>Viteria e bulloneria</t>
-  </si>
-  <si>
-    <t>Lavaggio</t>
-  </si>
-  <si>
-    <t>Seghe e seghetti</t>
+    <t>Pitture murali</t>
   </si>
   <si>
     <t>Rubinetteria</t>
   </si>
   <si>
-    <t>Pinze e cesoie</t>
-  </si>
-  <si>
-    <t>Stucchi e siliconi</t>
-  </si>
-  <si>
-    <t>Bombole GPL gas</t>
-  </si>
-  <si>
-    <t>Tasselli e ancoraggi</t>
-  </si>
-  <si>
-    <t>Quadri elettrici e fusibili</t>
+    <t>Smalti e vernici legno</t>
+  </si>
+  <si>
+    <t>Contenitori e organizzazione</t>
+  </si>
+  <si>
+    <t>Cemento e malte</t>
+  </si>
+  <si>
+    <t>Lavastoviglie</t>
+  </si>
+  <si>
+    <t>Sifoni e scarichi</t>
+  </si>
+  <si>
+    <t>Cancelleria e ufficio</t>
+  </si>
+  <si>
+    <t>Cucine</t>
+  </si>
+  <si>
+    <t>Guarnizioni</t>
+  </si>
+  <si>
+    <t>Martelli e mazze</t>
+  </si>
+  <si>
+    <t>Solventi e diluenti</t>
+  </si>
+  <si>
+    <t>Pulizia</t>
+  </si>
+  <si>
+    <t>Catene e corde</t>
+  </si>
+  <si>
+    <t>Fusibili e quadri</t>
+  </si>
+  <si>
+    <t>Pompe</t>
+  </si>
+  <si>
+    <t>Nastri e teli protettivi</t>
+  </si>
+  <si>
+    <t>Articoli stagionali</t>
+  </si>
+  <si>
+    <t>Torce e pile</t>
+  </si>
+  <si>
+    <t>Teflon e sigillanti</t>
+  </si>
+  <si>
+    <t>Stucchi e decorazioni</t>
+  </si>
+  <si>
+    <t>Set e valigette</t>
+  </si>
+  <si>
+    <t>Tinte decorative</t>
+  </si>
+  <si>
+    <t>Climatizzazione</t>
   </si>
   <si>
     <t>Riscaldamento</t>
   </si>
   <si>
-    <t>Martelli e scalpelli</t>
-  </si>
-  <si>
-    <t>Diluenti e solventi</t>
-  </si>
-  <si>
-    <t>Raccorderia</t>
-  </si>
-  <si>
-    <t>Sicurezza e serrature</t>
-  </si>
-  <si>
-    <t>Categoria Esempio</t>
-  </si>
-  <si>
-    <t>Climatizzazione</t>
-  </si>
-  <si>
-    <t>Strumenti di misura</t>
-  </si>
-  <si>
-    <t>Vernici speciali</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/9008764/gallery_isolante-fissativo-ad-acqua-lt-4-antimuffa-bianco-polare.jpg</t>
-  </si>
-  <si>
-    <t>Tassello nylon 'GL-5VPS' c/vite 4,0 x 30 '65005'</t>
-  </si>
-  <si>
-    <t>Appendiabito doppio 'Dubbel' - cm 80 x 42 x H90 c/ruote nero</t>
-  </si>
-  <si>
-    <t>Convertiruggine FEROX</t>
-  </si>
-  <si>
-    <t>varianti: 95 ml = xx.xx | 375 ml = xx.xx | 750 ml = xx.xx</t>
-  </si>
-  <si>
-    <t>Maniglia goccia c/ros. bocchetta cromo satinato</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/3020052/gallery_maniglia-goccia-c-ros-bocchetta-cromo-satinato.jpg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/FE1240/gallery_1240.jpg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/920010/gallery_ferox-convertiruggine-ml-95-art-4143.jpg | https://b2b.dfl.it//sites/default/files//product_images/920011/gallery_ferox-convertiruggine-ml-375-art-4148.jpg | https://b2b.dfl.it//sites/default/files//product_images/920012/gallery_ferox-convertiruggine-ml-750-art-4145.jpg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/EF0002/gallery_0002.jpg</t>
-  </si>
-  <si>
-    <t>Stucco 'K2' in polvere per interni - 20 kg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0164/gallery_0164.jpg</t>
-  </si>
-  <si>
-    <t>Stucco 'super stucco' 'fassa bortolo' - 10 kg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0710/gallery_0710.jpg</t>
-  </si>
-  <si>
-    <t>Idropittura bianco polare antimuffa - 4 LT, semilavabile per interni, trasp.</t>
-  </si>
-  <si>
-    <t>Isolante fissativo ad acqua antimuffa bianco polare - 4 LT</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/CC0136/gallery_0136.jpg</t>
-  </si>
-  <si>
-    <t>Carbone vegetale per grill - 5 kg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/700872/gallery_carbone-vegetale-x-grill-kg-5-ca-in-sacchi.jpg</t>
-  </si>
-  <si>
-    <t>Pistola per silico 'UNIKO' avanzamento a friz.</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/UM1521/gallery_pistola-per-silicone-a-frizione-uniko-all-e-ferro.jpg</t>
-  </si>
-  <si>
-    <t>Fornello elettrico 2 piastre - 1500 + 1000 W, D. 15,5 + 18,5 c/termost. regol.</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/CA2008/gallery_fornello-elettrico-2-piastre-1500-1000w-d-15-5-18-5-c-termost-regol.jpg</t>
-  </si>
-  <si>
-    <t>Insetticida spray per vespe - 750 ml</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/TL0768/gallery_0768.jpg</t>
-  </si>
-  <si>
-    <t>Punta widia 'SDX' 4 x 75 mm per muro FISCHER</t>
-  </si>
-  <si>
-    <t>Accessori</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/UM0091/gallery_0091.jpg</t>
-  </si>
-  <si>
-    <t>Punta carburo 'S-SDX' 5 x 85 mm 4 taglienti FISCHER</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/UM0092/gallery_0092.jpg</t>
-  </si>
-  <si>
-    <t>Lampadina LED 'sfera' 8 W E14</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0380/gallery_0380.jpg</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0389/gallery_0389.jpg</t>
-  </si>
-  <si>
-    <t>Lampadina LED 'oliva' 8 W 806 LM-6500K fredda 60 W</t>
-  </si>
-  <si>
-    <t>Lampada LED 'spot' GU10/6 W 490 LM-4000K naturale 40 W</t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0394/gallery_0394.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adattatore 2+1 schuko 2P+T10A SP.2P+T10A </t>
-  </si>
-  <si>
-    <t>https://b2b.dfl.it//sites/default/files//product_images/ME0187/gallery_0187.jpg</t>
+    <t>Ricambi e accessori</t>
+  </si>
+  <si>
+    <t>Cura della persona</t>
+  </si>
+  <si>
+    <t>Pistola per silicone 'UNIKO' avanzamento a friz.</t>
   </si>
 </sst>
 </file>
@@ -814,7 +829,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -832,52 +847,6 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF212529"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -893,7 +862,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -916,32 +885,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -955,37 +903,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1286,19 +1205,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="66" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="56" customWidth="1"/>
+    <col min="5" max="5" width="344" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1320,169 +1239,144 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D2" s="4">
         <v>4.2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="4">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="4">
         <v>32</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D5" s="4">
         <v>59</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="4">
         <v>2.5</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" t="s">
-        <v>210</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" t="s">
-        <v>225</v>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{F37CC63A-B512-4240-BE7F-008CE441A199}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$A$2:$A$10</xm:f>
+            <xm:f>Sottocategorie!$A$2:$A$9</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -1494,18 +1388,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="8" width="15" customWidth="1"/>
+    <col min="5" max="5" width="82" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1527,214 +1421,189 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D2" s="4">
         <v>22.9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="E2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3" s="4">
         <v>29.9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4">
         <v>9.9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4">
         <v>7.9</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="D6" s="4">
         <v>10.9</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4">
         <v>12.9</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="B11" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>258</v>
-      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F9" r:id="rId1" xr:uid="{7D0C8A39-A651-494B-9328-D32669CA1086}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$B$2:$B$7</xm:f>
+            <xm:f>Sottocategorie!$B$2:$B$8</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -1746,19 +1615,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="61" customWidth="1"/>
+    <col min="2" max="2" width="81" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="8" width="15" customWidth="1"/>
+    <col min="5" max="5" width="145" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1779,502 +1648,429 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D2" s="4">
         <v>429</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D3" s="4">
         <v>419</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
+      <c r="E3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4">
         <v>299</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="E4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4">
         <v>299</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="E5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4">
         <v>149</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D7" s="4">
         <v>149</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D8" s="4">
         <v>469</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="D9" s="4">
         <v>269</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="E9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D10" s="4">
         <v>219</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="E10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D11" s="4">
         <v>619</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="E11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D12" s="4">
         <v>339</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="E12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D13" s="4">
         <v>269</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="E13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D14" s="4">
         <v>569</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="E14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D15" s="4">
         <v>449</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="E15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D16" s="4">
         <v>599</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="E16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D17" s="4">
         <v>269</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="E17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D18" s="4">
         <v>149</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="E18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4">
         <v>239</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="E19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D20" s="4">
         <v>469</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D21" s="4">
         <v>369</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="E21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D22" s="4">
         <v>118</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="E22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B23" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>243</v>
-      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1" xr:uid="{367224B6-2298-485B-9A36-A0F2EACB1430}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$C$2:$C$10</xm:f>
+            <xm:f>Sottocategorie!$C$2:$C$13</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -2286,19 +2082,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="88" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="5" max="5" width="82" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2320,383 +2116,332 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D2" s="4">
         <v>91</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="E2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D3" s="4">
         <v>36.9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>90</v>
-      </c>
+      <c r="E3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D4" s="4">
         <v>91.9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>92</v>
-      </c>
+      <c r="E4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D5" s="4">
         <v>58.9</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="E5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>97</v>
+        <v>109</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D6" s="4">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="E6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D7" s="4">
         <v>43.5</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D8" s="4">
         <v>75.900000000000006</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="E8" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D9" s="4">
         <v>45.9</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="E9" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D10" s="4">
         <v>28.5</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="E10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D11" s="4">
         <v>41.9</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>108</v>
-      </c>
+      <c r="E11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D12" s="4">
         <v>104.9</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="E12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D13" s="4">
         <v>36</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D14" s="4">
         <v>22</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="E14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4">
         <v>91.5</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="E15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" s="4">
         <v>21</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>121</v>
-      </c>
+      <c r="E16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="2:6" ht="15" x14ac:dyDescent="0.3">
-      <c r="B17" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="B18" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>250</v>
-      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0300-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0300-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$D$2:$D$9</xm:f>
+            <xm:f>Sottocategorie!$D$2:$D$8</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -2708,20 +2453,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="4" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2742,71 +2485,57 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4">
         <v>31</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D3" s="4">
         <v>3.9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>130</v>
+      <c r="E3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0400-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0400-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$E$2:$E$7</xm:f>
+            <xm:f>Sottocategorie!$E$2:$E$10</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -2818,19 +2547,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="93" customWidth="1"/>
+    <col min="5" max="5" width="127" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="93" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2852,311 +2581,268 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D2" s="4">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="E2" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D3" s="4">
         <v>5.3</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>134</v>
-      </c>
+      <c r="E3" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D4" s="4">
         <v>2.1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D5" s="4">
         <v>1.8</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="D6" s="4">
         <v>1.8</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D7" s="4">
         <v>6.8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>146</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D8" s="4">
         <v>7.6</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="E8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D9" s="4">
         <v>14</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>151</v>
-      </c>
+      <c r="E9" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D10" s="4">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>154</v>
-      </c>
+      <c r="E10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4">
         <v>15</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>157</v>
-      </c>
+      <c r="E11" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4">
         <v>4.5</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="E12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D13" s="4">
         <v>3.6</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="B14" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>241</v>
-      </c>
+      <c r="E13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0500-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$F$2:$F$13</xm:f>
+            <xm:f>Sottocategorie!$F$2:$F$9</xm:f>
           </x14:formula1>
-          <xm:sqref>C16:C200 C2:C14</xm:sqref>
+          <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3166,19 +2852,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="2" max="2" width="79" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="107" customWidth="1"/>
+    <col min="5" max="5" width="135" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="107" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3200,150 +2886,117 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D2" s="4">
         <v>1.5</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>169</v>
+        <v>187</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D3" s="4">
         <v>0.9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" s="12"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="G6" s="12"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="B9" s="12"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="B14" s="12"/>
+      <c r="E3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0600-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{4E48EF9E-C178-4E32-8BAB-6504F4A6325B}"/>
-    <hyperlink ref="F6" r:id="rId2" xr:uid="{F6E7DF7D-9EE1-47BE-B14B-410D0613DEDA}"/>
-    <hyperlink ref="F7" r:id="rId3" xr:uid="{819384DA-32A7-4E33-BAA5-7313F4C1EC2F}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0600-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$G$2:$G$6</xm:f>
+            <xm:f>Sottocategorie!$G$2:$G$10</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -3355,19 +3008,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="2" max="2" width="63" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="68" customWidth="1"/>
+    <col min="5" max="5" width="125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3389,239 +3042,210 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D2" s="4">
         <v>159</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="E2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D3" s="4">
         <v>13.9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>174</v>
-      </c>
+      <c r="E3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D4" s="4">
         <v>0.8</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>176</v>
-      </c>
+      <c r="E4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D5" s="4">
         <v>16.899999999999999</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D6" s="4">
         <v>5.5</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="E6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D7" s="4">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>184</v>
-      </c>
+      <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="D8" s="4">
         <v>24.9</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>186</v>
-      </c>
+      <c r="E8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B9" s="8" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.35">
-      <c r="B12" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>245</v>
-      </c>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Disponibilità non valida" error="Seleziona uno stato di disponibilità valido" promptTitle="Disponibilità" prompt="Scegli lo stato di disponibilità" sqref="E2:E200" xr:uid="{00000000-0002-0000-0700-000001000000}">
-      <formula1>"Disponibile,In Arrivo,Esaurito,Contattare Negozio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F10" r:id="rId1" xr:uid="{0E4A3288-AA6B-4366-9303-E25D651B7318}"/>
-    <hyperlink ref="F11" r:id="rId2" xr:uid="{5FE59A63-F362-4934-B213-6AD8618465DD}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Sottocategoria non valida" error="Seleziona una sottocategoria valida dalla lista" promptTitle="Sottocategoria" prompt="Scegli una sottocategoria dalla lista" xr:uid="{00000000-0002-0000-0700-000000000000}">
           <x14:formula1>
-            <xm:f>Sottocategorie!$H$2:$H$6</xm:f>
+            <xm:f>Sottocategorie!$H$2:$H$8</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C200</xm:sqref>
         </x14:dataValidation>
@@ -3638,232 +3262,253 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="B1" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="C1" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="D1" t="s">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="E1" t="s">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="F1" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="G1" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="H1" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="F3" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="G3" t="s">
-        <v>166</v>
+        <v>238</v>
       </c>
       <c r="H3" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>205</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="F4" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="G4" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="H4" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>210</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="G5" t="s">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="H5" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="F6" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="G6" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="H6" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
-        <v>217</v>
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>143</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>257</v>
+      </c>
+      <c r="G8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
+        <v>259</v>
+      </c>
+      <c r="E9" t="s">
+        <v>147</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" t="s">
-        <v>148</v>
+        <v>260</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F11" t="s">
-        <v>153</v>
+      <c r="C11" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F12" t="s">
-        <v>156</v>
+      <c r="C12" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F13" t="s">
-        <v>23</v>
+      <c r="C13" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
